--- a/Team-Data/2014-15/4-11-2014-15.xlsx
+++ b/Team-Data/2014-15/4-11-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>5.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AE2" t="n">
         <v>2</v>
@@ -766,7 +833,7 @@
         <v>4</v>
       </c>
       <c r="AM2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN2" t="n">
         <v>2</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-0.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
         <v>17</v>
@@ -933,7 +1000,7 @@
         <v>17</v>
       </c>
       <c r="AH3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI3" t="n">
         <v>5</v>
@@ -957,10 +1024,10 @@
         <v>28</v>
       </c>
       <c r="AP3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR3" t="n">
         <v>11</v>
@@ -969,7 +1036,7 @@
         <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AU3" t="n">
         <v>5</v>
@@ -984,7 +1051,7 @@
         <v>30</v>
       </c>
       <c r="AY3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ3" t="n">
         <v>22</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AE4" t="n">
         <v>17</v>
@@ -1115,10 +1182,10 @@
         <v>17</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ4" t="n">
         <v>17</v>
@@ -1145,7 +1212,7 @@
         <v>20</v>
       </c>
       <c r="AR4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS4" t="n">
         <v>17</v>
@@ -1160,7 +1227,7 @@
         <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX4" t="n">
         <v>25</v>
@@ -1175,7 +1242,7 @@
         <v>18</v>
       </c>
       <c r="BB4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC4" t="n">
         <v>21</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-2.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
@@ -1312,7 +1379,7 @@
         <v>27</v>
       </c>
       <c r="AM5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AN5" t="n">
         <v>30</v>
@@ -1354,7 +1421,7 @@
         <v>4</v>
       </c>
       <c r="BA5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB5" t="n">
         <v>27</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
@@ -1389,25 +1456,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F6" t="n">
         <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6</v>
+        <v>0.595</v>
       </c>
       <c r="H6" t="n">
         <v>48.5</v>
       </c>
       <c r="I6" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J6" t="n">
-        <v>82.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="K6" t="n">
         <v>0.441</v>
@@ -1419,16 +1486,16 @@
         <v>22.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="O6" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="P6" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.782</v>
+        <v>0.784</v>
       </c>
       <c r="R6" t="n">
         <v>11.8</v>
@@ -1443,7 +1510,7 @@
         <v>21.8</v>
       </c>
       <c r="V6" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W6" t="n">
         <v>6.2</v>
@@ -1458,19 +1525,19 @@
         <v>18.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.8</v>
+        <v>100.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF6" t="n">
         <v>10</v>
@@ -1479,13 +1546,13 @@
         <v>10</v>
       </c>
       <c r="AH6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AI6" t="n">
         <v>23</v>
       </c>
       <c r="AJ6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK6" t="n">
         <v>22</v>
@@ -1503,7 +1570,7 @@
         <v>3</v>
       </c>
       <c r="AP6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ6" t="n">
         <v>3</v>
@@ -1524,19 +1591,19 @@
         <v>13</v>
       </c>
       <c r="AW6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX6" t="n">
         <v>5</v>
       </c>
       <c r="AY6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ6" t="n">
         <v>3</v>
       </c>
       <c r="BA6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB6" t="n">
         <v>15</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>4.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
         <v>7</v>
@@ -1664,13 +1731,13 @@
         <v>24</v>
       </c>
       <c r="AI7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ7" t="n">
         <v>25</v>
       </c>
       <c r="AK7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL7" t="n">
         <v>4</v>
@@ -1679,7 +1746,7 @@
         <v>2</v>
       </c>
       <c r="AN7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO7" t="n">
         <v>7</v>
@@ -1688,7 +1755,7 @@
         <v>9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR7" t="n">
         <v>13</v>
@@ -1718,7 +1785,7 @@
         <v>5</v>
       </c>
       <c r="BA7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB7" t="n">
         <v>7</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E8" t="n">
         <v>48</v>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G8" t="n">
-        <v>0.615</v>
+        <v>0.608</v>
       </c>
       <c r="H8" t="n">
         <v>48.5</v>
@@ -1771,7 +1838,7 @@
         <v>39.7</v>
       </c>
       <c r="J8" t="n">
-        <v>86</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K8" t="n">
         <v>0.462</v>
@@ -1780,7 +1847,7 @@
         <v>8.9</v>
       </c>
       <c r="M8" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="N8" t="n">
         <v>0.349</v>
@@ -1792,19 +1859,19 @@
         <v>22.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.751</v>
+        <v>0.752</v>
       </c>
       <c r="R8" t="n">
         <v>10.5</v>
       </c>
       <c r="S8" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T8" t="n">
-        <v>42.3</v>
+        <v>42.1</v>
       </c>
       <c r="U8" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="V8" t="n">
         <v>12.9</v>
@@ -1825,13 +1892,13 @@
         <v>22.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>105.2</v>
+        <v>105.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1849,7 +1916,7 @@
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AK8" t="n">
         <v>6</v>
@@ -1870,13 +1937,13 @@
         <v>17</v>
       </c>
       <c r="AQ8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR8" t="n">
         <v>19</v>
       </c>
       <c r="AS8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT8" t="n">
         <v>23</v>
@@ -1885,13 +1952,13 @@
         <v>8</v>
       </c>
       <c r="AV8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
@@ -1906,7 +1973,7 @@
         <v>3</v>
       </c>
       <c r="BC8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-3.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
         <v>24</v>
@@ -2025,10 +2092,10 @@
         <v>24</v>
       </c>
       <c r="AH9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ9" t="n">
         <v>2</v>
@@ -2058,7 +2125,7 @@
         <v>3</v>
       </c>
       <c r="AS9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT9" t="n">
         <v>7</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-1.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2210,7 +2277,7 @@
         <v>17</v>
       </c>
       <c r="AI10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ10" t="n">
         <v>5</v>
@@ -2219,7 +2286,7 @@
         <v>27</v>
       </c>
       <c r="AL10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM10" t="n">
         <v>11</v>
@@ -2249,7 +2316,7 @@
         <v>17</v>
       </c>
       <c r="AV10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW10" t="n">
         <v>16</v>
@@ -2261,10 +2328,10 @@
         <v>17</v>
       </c>
       <c r="AZ10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB10" t="n">
         <v>21</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
@@ -2299,25 +2366,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F11" t="n">
         <v>15</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H11" t="n">
         <v>48.1</v>
       </c>
       <c r="I11" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="J11" t="n">
-        <v>87.2</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="K11" t="n">
         <v>0.477</v>
@@ -2326,7 +2393,7 @@
         <v>10.7</v>
       </c>
       <c r="M11" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="N11" t="n">
         <v>0.396</v>
@@ -2338,7 +2405,7 @@
         <v>20.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.769</v>
+        <v>0.77</v>
       </c>
       <c r="R11" t="n">
         <v>10.4</v>
@@ -2350,7 +2417,7 @@
         <v>44.8</v>
       </c>
       <c r="U11" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="V11" t="n">
         <v>14.4</v>
@@ -2359,7 +2426,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="X11" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Y11" t="n">
         <v>3.6</v>
@@ -2368,16 +2435,16 @@
         <v>19.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>109.7</v>
+        <v>109.6</v>
       </c>
       <c r="AC11" t="n">
         <v>10.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2389,7 +2456,7 @@
         <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI11" t="n">
         <v>1</v>
@@ -2446,7 +2513,7 @@
         <v>13</v>
       </c>
       <c r="BA11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB11" t="n">
         <v>1</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F12" t="n">
         <v>26</v>
       </c>
       <c r="G12" t="n">
-        <v>0.667</v>
+        <v>0.671</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J12" t="n">
-        <v>83.7</v>
+        <v>83.5</v>
       </c>
       <c r="K12" t="n">
         <v>0.442</v>
@@ -2508,16 +2575,16 @@
         <v>11.4</v>
       </c>
       <c r="M12" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="N12" t="n">
         <v>0.348</v>
       </c>
       <c r="O12" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="P12" t="n">
-        <v>25.3</v>
+        <v>25.6</v>
       </c>
       <c r="Q12" t="n">
         <v>0.715</v>
@@ -2526,7 +2593,7 @@
         <v>11.8</v>
       </c>
       <c r="S12" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T12" t="n">
         <v>43.6</v>
@@ -2538,7 +2605,7 @@
         <v>16.8</v>
       </c>
       <c r="W12" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="X12" t="n">
         <v>4.8</v>
@@ -2547,34 +2614,34 @@
         <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.5</v>
+        <v>103.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AD12" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="AE12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH12" t="n">
         <v>19</v>
       </c>
       <c r="AI12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ12" t="n">
         <v>12</v>
@@ -2589,13 +2656,13 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
         <v>6</v>
       </c>
       <c r="AP12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ12" t="n">
         <v>27</v>
@@ -2604,10 +2671,10 @@
         <v>6</v>
       </c>
       <c r="AS12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU12" t="n">
         <v>9</v>
@@ -2622,19 +2689,19 @@
         <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ12" t="n">
         <v>27</v>
       </c>
       <c r="BA12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
@@ -2741,19 +2808,19 @@
         <v>0.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AE13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF13" t="n">
         <v>19</v>
       </c>
       <c r="AG13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
         <v>24</v>
@@ -2783,7 +2850,7 @@
         <v>14</v>
       </c>
       <c r="AR13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS13" t="n">
         <v>4</v>
@@ -2798,10 +2865,10 @@
         <v>14</v>
       </c>
       <c r="AW13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY13" t="n">
         <v>15</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E14" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F14" t="n">
         <v>26</v>
       </c>
       <c r="G14" t="n">
-        <v>0.675</v>
+        <v>0.671</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
@@ -2863,10 +2930,10 @@
         <v>39.4</v>
       </c>
       <c r="J14" t="n">
-        <v>83.3</v>
+        <v>83.2</v>
       </c>
       <c r="K14" t="n">
-        <v>0.473</v>
+        <v>0.474</v>
       </c>
       <c r="L14" t="n">
         <v>10.1</v>
@@ -2875,7 +2942,7 @@
         <v>26.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.376</v>
+        <v>0.378</v>
       </c>
       <c r="O14" t="n">
         <v>17.8</v>
@@ -2884,7 +2951,7 @@
         <v>25.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.709</v>
+        <v>0.708</v>
       </c>
       <c r="R14" t="n">
         <v>9.5</v>
@@ -2893,10 +2960,10 @@
         <v>33.1</v>
       </c>
       <c r="T14" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="U14" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="V14" t="n">
         <v>12.3</v>
@@ -2905,7 +2972,7 @@
         <v>7.8</v>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y14" t="n">
         <v>3</v>
@@ -2914,34 +2981,34 @@
         <v>21.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>106.6</v>
+        <v>106.8</v>
       </c>
       <c r="AC14" t="n">
         <v>6.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI14" t="n">
         <v>3</v>
       </c>
       <c r="AJ14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK14" t="n">
         <v>2</v>
@@ -2959,7 +3026,7 @@
         <v>8</v>
       </c>
       <c r="AP14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ14" t="n">
         <v>28</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E15" t="n">
         <v>21</v>
       </c>
       <c r="F15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>0.269</v>
+        <v>0.266</v>
       </c>
       <c r="H15" t="n">
         <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J15" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="K15" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L15" t="n">
         <v>6.5</v>
       </c>
       <c r="M15" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0.346</v>
+        <v>0.345</v>
       </c>
       <c r="O15" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="P15" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.738</v>
+        <v>0.739</v>
       </c>
       <c r="R15" t="n">
         <v>11.6</v>
       </c>
       <c r="S15" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T15" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="U15" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V15" t="n">
         <v>13.2</v>
@@ -3087,25 +3154,25 @@
         <v>7.1</v>
       </c>
       <c r="X15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y15" t="n">
         <v>4.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>98.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.4</v>
+        <v>-6.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3132,7 +3199,7 @@
         <v>25</v>
       </c>
       <c r="AM15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AN15" t="n">
         <v>16</v>
@@ -3141,7 +3208,7 @@
         <v>12</v>
       </c>
       <c r="AP15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ15" t="n">
         <v>23</v>
@@ -3150,10 +3217,10 @@
         <v>9</v>
       </c>
       <c r="AS15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT15" t="n">
         <v>12</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>11</v>
       </c>
       <c r="AU15" t="n">
         <v>21</v>
@@ -3168,16 +3235,16 @@
         <v>22</v>
       </c>
       <c r="AY15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BB15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E16" t="n">
         <v>54</v>
       </c>
       <c r="F16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G16" t="n">
-        <v>0.675</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H16" t="n">
         <v>48.6</v>
@@ -3230,16 +3297,16 @@
         <v>82.40000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L16" t="n">
         <v>5.2</v>
       </c>
       <c r="M16" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0.34</v>
+        <v>0.341</v>
       </c>
       <c r="O16" t="n">
         <v>17.6</v>
@@ -3248,7 +3315,7 @@
         <v>22.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.772</v>
+        <v>0.774</v>
       </c>
       <c r="R16" t="n">
         <v>10.3</v>
@@ -3260,7 +3327,7 @@
         <v>42.5</v>
       </c>
       <c r="U16" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V16" t="n">
         <v>13.3</v>
@@ -3281,13 +3348,13 @@
         <v>20.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>98.3</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3299,7 +3366,7 @@
         <v>3</v>
       </c>
       <c r="AH16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI16" t="n">
         <v>12</v>
@@ -3308,7 +3375,7 @@
         <v>22</v>
       </c>
       <c r="AK16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL16" t="n">
         <v>29</v>
@@ -3317,7 +3384,7 @@
         <v>29</v>
       </c>
       <c r="AN16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO16" t="n">
         <v>10</v>
@@ -3326,7 +3393,7 @@
         <v>15</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR16" t="n">
         <v>23</v>
@@ -3338,7 +3405,7 @@
         <v>21</v>
       </c>
       <c r="AU16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV16" t="n">
         <v>6</v>
@@ -3359,7 +3426,7 @@
         <v>16</v>
       </c>
       <c r="BB16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC16" t="n">
         <v>7</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E17" t="n">
         <v>35</v>
       </c>
       <c r="F17" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G17" t="n">
-        <v>0.438</v>
+        <v>0.443</v>
       </c>
       <c r="H17" t="n">
         <v>48.1</v>
@@ -3409,7 +3476,7 @@
         <v>35.1</v>
       </c>
       <c r="J17" t="n">
-        <v>77</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K17" t="n">
         <v>0.456</v>
@@ -3421,31 +3488,31 @@
         <v>20.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0.334</v>
+        <v>0.335</v>
       </c>
       <c r="O17" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="P17" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.74</v>
+        <v>0.745</v>
       </c>
       <c r="R17" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="S17" t="n">
         <v>29.9</v>
       </c>
       <c r="T17" t="n">
-        <v>39</v>
+        <v>38.8</v>
       </c>
       <c r="U17" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="V17" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W17" t="n">
         <v>7.9</v>
@@ -3457,19 +3524,19 @@
         <v>4.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>94.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC17" t="n">
         <v>-2.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE17" t="n">
         <v>21</v>
@@ -3481,10 +3548,10 @@
         <v>21</v>
       </c>
       <c r="AH17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3493,7 +3560,7 @@
         <v>11</v>
       </c>
       <c r="AL17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM17" t="n">
         <v>19</v>
@@ -3502,13 +3569,13 @@
         <v>24</v>
       </c>
       <c r="AO17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR17" t="n">
         <v>29</v>
@@ -3520,16 +3587,16 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AV17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX17" t="n">
         <v>20</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>19</v>
       </c>
       <c r="AY17" t="n">
         <v>8</v>
@@ -3538,7 +3605,7 @@
         <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB17" t="n">
         <v>28</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>0.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AE18" t="n">
         <v>15</v>
@@ -3663,7 +3730,7 @@
         <v>15</v>
       </c>
       <c r="AH18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI18" t="n">
         <v>18</v>
@@ -3681,7 +3748,7 @@
         <v>26</v>
       </c>
       <c r="AN18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO18" t="n">
         <v>22</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E19" t="n">
         <v>16</v>
       </c>
       <c r="F19" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2</v>
+        <v>0.203</v>
       </c>
       <c r="H19" t="n">
         <v>48.3</v>
@@ -3773,19 +3840,19 @@
         <v>36.5</v>
       </c>
       <c r="J19" t="n">
-        <v>83.2</v>
+        <v>83.3</v>
       </c>
       <c r="K19" t="n">
         <v>0.438</v>
       </c>
       <c r="L19" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="M19" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.333</v>
+        <v>0.33</v>
       </c>
       <c r="O19" t="n">
         <v>19.8</v>
@@ -3821,19 +3888,19 @@
         <v>5.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AA19" t="n">
         <v>21.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>97.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-8.6</v>
+        <v>-8.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE19" t="n">
         <v>29</v>
@@ -3845,13 +3912,13 @@
         <v>29</v>
       </c>
       <c r="AH19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI19" t="n">
         <v>25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
@@ -3869,7 +3936,7 @@
         <v>2</v>
       </c>
       <c r="AP19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ19" t="n">
         <v>6</v>
@@ -3899,7 +3966,7 @@
         <v>26</v>
       </c>
       <c r="AZ19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA19" t="n">
         <v>5</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
@@ -3937,55 +4004,55 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E20" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F20" t="n">
         <v>36</v>
       </c>
       <c r="G20" t="n">
-        <v>0.538</v>
+        <v>0.544</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J20" t="n">
-        <v>82.5</v>
+        <v>82.7</v>
       </c>
       <c r="K20" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L20" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M20" t="n">
         <v>19.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.371</v>
+        <v>0.37</v>
       </c>
       <c r="O20" t="n">
         <v>16.4</v>
       </c>
       <c r="P20" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.757</v>
+        <v>0.752</v>
       </c>
       <c r="R20" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S20" t="n">
         <v>32.1</v>
       </c>
       <c r="T20" t="n">
-        <v>43.4</v>
+        <v>43.7</v>
       </c>
       <c r="U20" t="n">
         <v>22.1</v>
@@ -3997,10 +4064,10 @@
         <v>6.7</v>
       </c>
       <c r="X20" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z20" t="n">
         <v>18.5</v>
@@ -4009,22 +4076,22 @@
         <v>18.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>99</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="AE20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF20" t="n">
         <v>13</v>
       </c>
       <c r="AG20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH20" t="n">
         <v>23</v>
@@ -4033,7 +4100,7 @@
         <v>13</v>
       </c>
       <c r="AJ20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK20" t="n">
         <v>10</v>
@@ -4054,7 +4121,7 @@
         <v>20</v>
       </c>
       <c r="AQ20" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AR20" t="n">
         <v>10</v>
@@ -4063,13 +4130,13 @@
         <v>16</v>
       </c>
       <c r="AT20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU20" t="n">
         <v>10</v>
       </c>
       <c r="AV20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW20" t="n">
         <v>25</v>
@@ -4084,7 +4151,7 @@
         <v>6</v>
       </c>
       <c r="BA20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB20" t="n">
         <v>16</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F21" t="n">
         <v>64</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="H21" t="n">
         <v>48.4</v>
@@ -4140,7 +4207,7 @@
         <v>82.2</v>
       </c>
       <c r="K21" t="n">
-        <v>0.427</v>
+        <v>0.428</v>
       </c>
       <c r="L21" t="n">
         <v>6.8</v>
@@ -4149,25 +4216,25 @@
         <v>19.6</v>
       </c>
       <c r="N21" t="n">
-        <v>0.344</v>
+        <v>0.345</v>
       </c>
       <c r="O21" t="n">
         <v>14.8</v>
       </c>
       <c r="P21" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.772</v>
+        <v>0.771</v>
       </c>
       <c r="R21" t="n">
         <v>10.6</v>
       </c>
       <c r="S21" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="T21" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="U21" t="n">
         <v>21.2</v>
@@ -4176,43 +4243,43 @@
         <v>14.6</v>
       </c>
       <c r="W21" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X21" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y21" t="n">
         <v>4.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AA21" t="n">
         <v>19.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>91.7</v>
+        <v>91.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AH21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ21" t="n">
         <v>24</v>
@@ -4227,7 +4294,7 @@
         <v>21</v>
       </c>
       <c r="AN21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
@@ -4236,7 +4303,7 @@
         <v>29</v>
       </c>
       <c r="AQ21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR21" t="n">
         <v>18</v>
@@ -4254,7 +4321,7 @@
         <v>19</v>
       </c>
       <c r="AW21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX21" t="n">
         <v>14</v>
@@ -4269,7 +4336,7 @@
         <v>25</v>
       </c>
       <c r="BB21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC21" t="n">
         <v>30</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>2</v>
       </c>
       <c r="AD22" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
         <v>13</v>
@@ -4433,7 +4500,7 @@
         <v>24</v>
       </c>
       <c r="AV22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW22" t="n">
         <v>21</v>
@@ -4451,7 +4518,7 @@
         <v>13</v>
       </c>
       <c r="BB22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC22" t="n">
         <v>12</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
@@ -4510,28 +4577,28 @@
         <v>6.8</v>
       </c>
       <c r="M23" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0.347</v>
+        <v>0.349</v>
       </c>
       <c r="O23" t="n">
         <v>14</v>
       </c>
       <c r="P23" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="Q23" t="n">
         <v>0.734</v>
       </c>
       <c r="R23" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S23" t="n">
         <v>31.7</v>
       </c>
       <c r="T23" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
       <c r="U23" t="n">
         <v>20.8</v>
@@ -4546,22 +4613,22 @@
         <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="AB23" t="n">
         <v>96</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.5</v>
+        <v>-5.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4576,10 +4643,10 @@
         <v>24</v>
       </c>
       <c r="AI23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK23" t="n">
         <v>13</v>
@@ -4591,7 +4658,7 @@
         <v>22</v>
       </c>
       <c r="AN23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO23" t="n">
         <v>30</v>
@@ -4603,13 +4670,13 @@
         <v>24</v>
       </c>
       <c r="AR23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU23" t="n">
         <v>22</v>
@@ -4618,16 +4685,16 @@
         <v>22</v>
       </c>
       <c r="AW23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX23" t="n">
         <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
@@ -4665,34 +4732,34 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E24" t="n">
         <v>18</v>
       </c>
       <c r="F24" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G24" t="n">
-        <v>0.225</v>
+        <v>0.228</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="J24" t="n">
-        <v>82.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0.408</v>
+        <v>0.407</v>
       </c>
       <c r="L24" t="n">
         <v>8.5</v>
       </c>
       <c r="M24" t="n">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
       <c r="N24" t="n">
         <v>0.324</v>
@@ -4704,25 +4771,25 @@
         <v>23.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.672</v>
+        <v>0.67</v>
       </c>
       <c r="R24" t="n">
         <v>11.9</v>
       </c>
       <c r="S24" t="n">
-        <v>31</v>
+        <v>30.9</v>
       </c>
       <c r="T24" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="U24" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V24" t="n">
         <v>17.6</v>
       </c>
       <c r="W24" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="X24" t="n">
         <v>6</v>
@@ -4731,19 +4798,19 @@
         <v>5.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AA24" t="n">
         <v>20.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>91.8</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>-9</v>
+        <v>-9.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4755,13 +4822,13 @@
         <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
       </c>
       <c r="AJ24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK24" t="n">
         <v>30</v>
@@ -4776,10 +4843,10 @@
         <v>28</v>
       </c>
       <c r="AO24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
@@ -4803,7 +4870,7 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY24" t="n">
         <v>27</v>
@@ -4815,7 +4882,7 @@
         <v>15</v>
       </c>
       <c r="BB24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC24" t="n">
         <v>29</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
@@ -4937,13 +5004,13 @@
         <v>16</v>
       </c>
       <c r="AH25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI25" t="n">
         <v>6</v>
       </c>
       <c r="AJ25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK25" t="n">
         <v>16</v>
@@ -4955,7 +5022,7 @@
         <v>9</v>
       </c>
       <c r="AN25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO25" t="n">
         <v>20</v>
@@ -4970,7 +5037,7 @@
         <v>14</v>
       </c>
       <c r="AS25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT25" t="n">
         <v>17</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E26" t="n">
         <v>51</v>
       </c>
       <c r="F26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G26" t="n">
-        <v>0.638</v>
+        <v>0.646</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
@@ -5059,7 +5126,7 @@
         <v>27.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0.363</v>
+        <v>0.365</v>
       </c>
       <c r="O26" t="n">
         <v>15.6</v>
@@ -5074,10 +5141,10 @@
         <v>10.8</v>
       </c>
       <c r="S26" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="T26" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
       <c r="U26" t="n">
         <v>22</v>
@@ -5086,7 +5153,7 @@
         <v>13.6</v>
       </c>
       <c r="W26" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="X26" t="n">
         <v>4.6</v>
@@ -5104,28 +5171,28 @@
         <v>103</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
       </c>
       <c r="AF26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI26" t="n">
         <v>7</v>
       </c>
       <c r="AJ26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK26" t="n">
         <v>17</v>
@@ -5137,7 +5204,7 @@
         <v>3</v>
       </c>
       <c r="AN26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AO26" t="n">
         <v>27</v>
@@ -5149,7 +5216,7 @@
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS26" t="n">
         <v>1</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-4.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F28" t="n">
         <v>26</v>
       </c>
       <c r="G28" t="n">
-        <v>0.671</v>
+        <v>0.675</v>
       </c>
       <c r="H28" t="n">
         <v>48.7</v>
@@ -5411,7 +5478,7 @@
         <v>39.1</v>
       </c>
       <c r="J28" t="n">
-        <v>84</v>
+        <v>83.8</v>
       </c>
       <c r="K28" t="n">
         <v>0.466</v>
@@ -5423,16 +5490,16 @@
         <v>22.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.364</v>
+        <v>0.366</v>
       </c>
       <c r="O28" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="P28" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.778</v>
+        <v>0.779</v>
       </c>
       <c r="R28" t="n">
         <v>10</v>
@@ -5441,19 +5508,19 @@
         <v>33.8</v>
       </c>
       <c r="T28" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="U28" t="n">
         <v>24.3</v>
       </c>
       <c r="V28" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W28" t="n">
         <v>8.1</v>
       </c>
       <c r="X28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y28" t="n">
         <v>4.4</v>
@@ -5462,25 +5529,25 @@
         <v>19</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>103.2</v>
+        <v>103.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AE28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AF28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH28" t="n">
         <v>1</v>
@@ -5513,7 +5580,7 @@
         <v>4</v>
       </c>
       <c r="AR28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS28" t="n">
         <v>8</v>
@@ -5528,7 +5595,7 @@
         <v>12</v>
       </c>
       <c r="AW28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX28" t="n">
         <v>8</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
@@ -5575,22 +5642,22 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E29" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F29" t="n">
         <v>32</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6</v>
+        <v>0.595</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
       </c>
       <c r="I29" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="J29" t="n">
         <v>83.40000000000001</v>
@@ -5608,28 +5675,28 @@
         <v>0.352</v>
       </c>
       <c r="O29" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="P29" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.787</v>
+        <v>0.788</v>
       </c>
       <c r="R29" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S29" t="n">
         <v>30.8</v>
       </c>
       <c r="T29" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="U29" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V29" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W29" t="n">
         <v>7.5</v>
@@ -5638,25 +5705,25 @@
         <v>4.3</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z29" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>104.3</v>
+        <v>104.2</v>
       </c>
       <c r="AC29" t="n">
         <v>3.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF29" t="n">
         <v>10</v>
@@ -5665,7 +5732,7 @@
         <v>10</v>
       </c>
       <c r="AH29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI29" t="n">
         <v>11</v>
@@ -5695,19 +5762,19 @@
         <v>2</v>
       </c>
       <c r="AR29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS29" t="n">
         <v>27</v>
       </c>
       <c r="AT29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW29" t="n">
         <v>18</v>
@@ -5719,7 +5786,7 @@
         <v>19</v>
       </c>
       <c r="AZ29" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA29" t="n">
         <v>12</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E30" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F30" t="n">
         <v>43</v>
       </c>
       <c r="G30" t="n">
-        <v>0.463</v>
+        <v>0.456</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
@@ -5790,13 +5857,13 @@
         <v>0.344</v>
       </c>
       <c r="O30" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="P30" t="n">
-        <v>23.6</v>
+        <v>23.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.724</v>
+        <v>0.723</v>
       </c>
       <c r="R30" t="n">
         <v>12</v>
@@ -5826,19 +5893,19 @@
         <v>19.3</v>
       </c>
       <c r="AA30" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>95</v>
+        <v>94.8</v>
       </c>
       <c r="AC30" t="n">
         <v>0.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AF30" t="n">
         <v>19</v>
@@ -5865,13 +5932,13 @@
         <v>17</v>
       </c>
       <c r="AN30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO30" t="n">
         <v>14</v>
       </c>
       <c r="AP30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ30" t="n">
         <v>26</v>
@@ -5883,10 +5950,10 @@
         <v>20</v>
       </c>
       <c r="AT30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AV30" t="n">
         <v>26</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AE31" t="n">
         <v>12</v>
@@ -6029,7 +6096,7 @@
         <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI31" t="n">
         <v>9</v>
@@ -6050,16 +6117,16 @@
         <v>9</v>
       </c>
       <c r="AO31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP31" t="n">
         <v>22</v>
       </c>
       <c r="AQ31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS31" t="n">
         <v>6</v>
@@ -6083,13 +6150,13 @@
         <v>6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA31" t="n">
         <v>20</v>
       </c>
       <c r="BB31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC31" t="n">
         <v>13</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-11-2014-15</t>
+          <t>2015-04-11</t>
         </is>
       </c>
     </row>
